--- a/result.xlsx
+++ b/result.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHANU SURYAVANSHI\Desktop\new Excel Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FA84F3-1054-4EAE-B18B-691FD4A30A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91F01C6-1DDC-4CF9-9FE3-9EB2F0FF4516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{0E668913-53B6-4D4E-80DC-A3930A4C74DB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{0E668913-53B6-4D4E-80DC-A3930A4C74DB}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
     <sheet name="VLOOCKUP" sheetId="2" r:id="rId2"/>
     <sheet name="HLOOKUP" sheetId="3" r:id="rId3"/>
+    <sheet name="XLOOKUP" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="102">
   <si>
     <t>Roll No</t>
   </si>
@@ -309,6 +311,60 @@
   </si>
   <si>
     <t>HLOOKUP WITH MATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match ka use </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index Use </t>
+  </si>
+  <si>
+    <t>Index +Match</t>
+  </si>
+  <si>
+    <t>xlookup use whit roll no.</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>roll no.</t>
+  </si>
+  <si>
+    <t>xlookup only one value</t>
+  </si>
+  <si>
+    <t>xlookup multipul value</t>
+  </si>
+  <si>
+    <t>xlookup</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>VLOOKUP WITH APROXIMATE VALUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPROXIMATE MATCH IN VLOOKUP. </t>
+  </si>
+  <si>
+    <t>B) LOOKUP VALUE MUST BE GREATER THEN SMALLEST ELEMENT.</t>
+  </si>
+  <si>
+    <t>A)FIRST ARRANGE LOOKUP ARRY IN ASCENDING ORDER .</t>
   </si>
 </sst>
 </file>
@@ -946,7 +1002,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -955,6 +1011,15 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -998,6 +1063,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1426,26 +1504,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D5" s="2" t="s">
@@ -1527,14 +1605,14 @@
         <f>COUNTIF(F6:J6,"&lt;50")</f>
         <v>0</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="10"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="13"/>
     </row>
     <row r="7" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D7" s="1">
@@ -1578,12 +1656,12 @@
         <f t="shared" ref="O7:O55" si="3">COUNTIF(F7:J7,"&lt;50")</f>
         <v>0</v>
       </c>
-      <c r="R7" s="11"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="13"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="16"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D8" s="1">
@@ -3801,7 +3879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2747E55-D36D-4379-AC23-41AADD3CB7B9}">
-  <dimension ref="D4:T55"/>
+  <dimension ref="D4:U55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -3820,12 +3898,12 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:19" x14ac:dyDescent="0.3">
-      <c r="O4" s="16" t="s">
+      <c r="O4" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
     </row>
     <row r="5" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D5" s="4" t="s">
@@ -3849,10 +3927,10 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
     </row>
     <row r="6" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D6" s="4">
@@ -4051,12 +4129,12 @@
       <c r="J12" s="4">
         <v>62</v>
       </c>
-      <c r="O12" s="19" t="s">
+      <c r="O12" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
     </row>
     <row r="13" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D13" s="4">
@@ -4080,10 +4158,10 @@
       <c r="J13" s="4">
         <v>94</v>
       </c>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
     </row>
     <row r="14" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D14" s="4">
@@ -4240,10 +4318,10 @@
       <c r="J18" s="4">
         <v>67</v>
       </c>
-      <c r="N18" s="18" t="s">
+      <c r="N18" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="O18" s="17"/>
+      <c r="O18" s="20"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D19" s="4">
@@ -4267,8 +4345,8 @@
       <c r="J19" s="4">
         <v>52</v>
       </c>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D20" s="4">
@@ -4658,7 +4736,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D33" s="4">
         <v>28</v>
       </c>
@@ -4680,8 +4758,14 @@
       <c r="J33" s="4">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N33" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="O33" s="27"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="27"/>
+    </row>
+    <row r="34" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D34" s="4">
         <v>29</v>
       </c>
@@ -4703,8 +4787,12 @@
       <c r="J34" s="4">
         <v>71</v>
       </c>
-    </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="27"/>
+    </row>
+    <row r="35" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <v>30</v>
       </c>
@@ -4726,8 +4814,14 @@
       <c r="J35" s="4">
         <v>96</v>
       </c>
-    </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N35">
+        <v>34</v>
+      </c>
+      <c r="O35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <v>31</v>
       </c>
@@ -4749,8 +4843,21 @@
       <c r="J36" s="4">
         <v>53</v>
       </c>
-    </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N36">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>94</v>
+      </c>
+      <c r="P36">
+        <v>68</v>
+      </c>
+      <c r="Q36" t="str">
+        <f>VLOOKUP(P36,N35:O39,2,1)</f>
+        <v>E</v>
+      </c>
+    </row>
+    <row r="37" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D37" s="4">
         <v>32</v>
       </c>
@@ -4772,8 +4879,14 @@
       <c r="J37" s="4">
         <v>83</v>
       </c>
-    </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N37">
+        <v>58</v>
+      </c>
+      <c r="O37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D38" s="4">
         <v>33</v>
       </c>
@@ -4795,8 +4908,14 @@
       <c r="J38" s="4">
         <v>65</v>
       </c>
-    </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N38">
+        <v>59</v>
+      </c>
+      <c r="O38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D39" s="4">
         <v>34</v>
       </c>
@@ -4818,8 +4937,14 @@
       <c r="J39" s="4">
         <v>47</v>
       </c>
-    </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N39">
+        <v>68</v>
+      </c>
+      <c r="O39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D40" s="4">
         <v>35</v>
       </c>
@@ -4842,7 +4967,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D41" s="4">
         <v>36</v>
       </c>
@@ -4864,8 +4989,14 @@
       <c r="J41" s="4">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N41" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+    </row>
+    <row r="42" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D42" s="4">
         <v>37</v>
       </c>
@@ -4887,8 +5018,18 @@
       <c r="J42" s="4">
         <v>75</v>
       </c>
-    </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N42" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="28"/>
+    </row>
+    <row r="43" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
         <v>38</v>
       </c>
@@ -4910,8 +5051,18 @@
       <c r="J43" s="4">
         <v>40</v>
       </c>
-    </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="N43" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+    </row>
+    <row r="44" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D44" s="4">
         <v>39</v>
       </c>
@@ -4933,8 +5084,12 @@
       <c r="J44" s="4">
         <v>69</v>
       </c>
-    </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="R44" s="29"/>
+      <c r="S44" s="29"/>
+      <c r="T44" s="29"/>
+      <c r="U44" s="29"/>
+    </row>
+    <row r="45" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D45" s="4">
         <v>40</v>
       </c>
@@ -4957,7 +5112,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D46" s="4">
         <v>41</v>
       </c>
@@ -4980,7 +5135,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D47" s="4">
         <v>42</v>
       </c>
@@ -5003,7 +5158,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D48" s="4">
         <v>43</v>
       </c>
@@ -5188,10 +5343,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="O4:R5"/>
     <mergeCell ref="N18:O19"/>
     <mergeCell ref="O12:R13"/>
+    <mergeCell ref="N33:Q34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N8 N15 O20" xr:uid="{BDC4B10E-7A2F-4BBC-9E5F-488D043FB3A5}">
@@ -5221,7 +5377,7 @@
     <col min="10" max="11" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.88671875" style="5" bestFit="1" customWidth="1"/>
@@ -5276,12 +5432,12 @@
       <c r="G2" s="7">
         <v>75</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3" s="7">
@@ -5305,10 +5461,10 @@
       <c r="G3" s="7">
         <v>82</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="7">
@@ -5332,10 +5488,10 @@
       <c r="G4" s="7">
         <v>55</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="7">
@@ -5550,11 +5706,11 @@
       <c r="G10" s="7">
         <v>46</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="7">
@@ -5578,9 +5734,9 @@
       <c r="G11" s="7">
         <v>72</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="7">
@@ -5610,6 +5766,9 @@
       <c r="L12" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="N12" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13" s="7">
@@ -5742,11 +5901,11 @@
       <c r="G17" s="7">
         <v>86</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="7">
@@ -5770,9 +5929,9 @@
       <c r="G18" s="7">
         <v>64</v>
       </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="7">
@@ -6562,7 +6721,7 @@
     <mergeCell ref="J10:L11"/>
     <mergeCell ref="J17:L18"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J6 K13 K20" xr:uid="{D7A9CB20-E8BC-4E90-939C-58B96A0D1265}">
       <formula1>$C$1:$G$1</formula1>
     </dataValidation>
@@ -6572,4 +6731,1373 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7EA445-E06D-439C-A628-2FCB3E4CE723}">
+  <dimension ref="A1:P51"/>
+  <sheetFormatPr defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="5"/>
+    <col min="9" max="9" width="18.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="5"/>
+    <col min="12" max="12" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="5"/>
+    <col min="15" max="15" width="17.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>68</v>
+      </c>
+      <c r="D2" s="7">
+        <v>72</v>
+      </c>
+      <c r="E2" s="7">
+        <v>70</v>
+      </c>
+      <c r="F2" s="7">
+        <v>66</v>
+      </c>
+      <c r="G2" s="7">
+        <v>75</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7">
+        <v>74</v>
+      </c>
+      <c r="D3" s="7">
+        <v>81</v>
+      </c>
+      <c r="E3" s="7">
+        <v>78</v>
+      </c>
+      <c r="F3" s="7">
+        <v>76</v>
+      </c>
+      <c r="G3" s="7">
+        <v>82</v>
+      </c>
+      <c r="J3" s="5">
+        <f>INDEX(A1:G11,5,4)</f>
+        <v>88</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" s="26"/>
+      <c r="O3" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="P3" s="26"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45</v>
+      </c>
+      <c r="D4" s="7">
+        <v>52</v>
+      </c>
+      <c r="E4" s="7">
+        <v>48</v>
+      </c>
+      <c r="F4" s="7">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7">
+        <v>55</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7">
+        <v>82</v>
+      </c>
+      <c r="D5" s="7">
+        <v>88</v>
+      </c>
+      <c r="E5" s="7">
+        <v>85</v>
+      </c>
+      <c r="F5" s="7">
+        <v>80</v>
+      </c>
+      <c r="G5" s="7">
+        <v>90</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="5" cm="1">
+        <f t="array" ref="P5:P14">_xlfn.XLOOKUP(O5:O14,B2:B11,E2:E11)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7">
+        <v>34</v>
+      </c>
+      <c r="D6" s="7">
+        <v>42</v>
+      </c>
+      <c r="E6" s="7">
+        <v>38</v>
+      </c>
+      <c r="F6" s="7">
+        <v>40</v>
+      </c>
+      <c r="G6" s="7">
+        <v>45</v>
+      </c>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="5">
+        <f>_xlfn.XLOOKUP(L6,B2:B51,E2:E51)</f>
+        <v>70</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7">
+        <v>71</v>
+      </c>
+      <c r="D7" s="7">
+        <v>69</v>
+      </c>
+      <c r="E7" s="7">
+        <v>73</v>
+      </c>
+      <c r="F7" s="7">
+        <v>70</v>
+      </c>
+      <c r="G7" s="7">
+        <v>76</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7">
+        <v>58</v>
+      </c>
+      <c r="D8" s="7">
+        <v>61</v>
+      </c>
+      <c r="E8" s="7">
+        <v>60</v>
+      </c>
+      <c r="F8" s="7">
+        <v>57</v>
+      </c>
+      <c r="G8" s="7">
+        <v>62</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="5">
+        <f>INDEX(B1:G51,MATCH(I8,B1:B51,0),MATCH(J7,B1:G1,0))</f>
+        <v>81</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="7">
+        <v>89</v>
+      </c>
+      <c r="D9" s="7">
+        <v>92</v>
+      </c>
+      <c r="E9" s="7">
+        <v>90</v>
+      </c>
+      <c r="F9" s="7">
+        <v>88</v>
+      </c>
+      <c r="G9" s="7">
+        <v>94</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P9" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7">
+        <v>45</v>
+      </c>
+      <c r="E10" s="7">
+        <v>43</v>
+      </c>
+      <c r="F10" s="7">
+        <v>44</v>
+      </c>
+      <c r="G10" s="7">
+        <v>46</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P10" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="7">
+        <v>67</v>
+      </c>
+      <c r="D11" s="7">
+        <v>70</v>
+      </c>
+      <c r="E11" s="7">
+        <v>68</v>
+      </c>
+      <c r="F11" s="7">
+        <v>65</v>
+      </c>
+      <c r="G11" s="7">
+        <v>72</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="O11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7">
+        <v>76</v>
+      </c>
+      <c r="D12" s="7">
+        <v>80</v>
+      </c>
+      <c r="E12" s="7">
+        <v>78</v>
+      </c>
+      <c r="F12" s="7">
+        <v>75</v>
+      </c>
+      <c r="G12" s="7">
+        <v>82</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="O12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7">
+        <v>54</v>
+      </c>
+      <c r="D13" s="7">
+        <v>58</v>
+      </c>
+      <c r="E13" s="7">
+        <v>56</v>
+      </c>
+      <c r="F13" s="7">
+        <v>55</v>
+      </c>
+      <c r="G13" s="7">
+        <v>60</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="7">
+        <v>62</v>
+      </c>
+      <c r="D14" s="7">
+        <v>65</v>
+      </c>
+      <c r="E14" s="7">
+        <v>63</v>
+      </c>
+      <c r="F14" s="7">
+        <v>61</v>
+      </c>
+      <c r="G14" s="7">
+        <v>67</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="5">
+        <f>_xlfn.XLOOKUP(I14,B2:B51,A2:A51)</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="7">
+        <v>47</v>
+      </c>
+      <c r="D15" s="7">
+        <v>50</v>
+      </c>
+      <c r="E15" s="7">
+        <v>48</v>
+      </c>
+      <c r="F15" s="7">
+        <v>46</v>
+      </c>
+      <c r="G15" s="7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="7">
+        <v>35</v>
+      </c>
+      <c r="D16" s="7">
+        <v>38</v>
+      </c>
+      <c r="E16" s="7">
+        <v>40</v>
+      </c>
+      <c r="F16" s="7">
+        <v>37</v>
+      </c>
+      <c r="G16" s="7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="7">
+        <v>81</v>
+      </c>
+      <c r="D17" s="7">
+        <v>84</v>
+      </c>
+      <c r="E17" s="7">
+        <v>83</v>
+      </c>
+      <c r="F17" s="7">
+        <v>80</v>
+      </c>
+      <c r="G17" s="7">
+        <v>86</v>
+      </c>
+      <c r="L17" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="M17" s="26"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="7">
+        <v>59</v>
+      </c>
+      <c r="D18" s="7">
+        <v>62</v>
+      </c>
+      <c r="E18" s="7">
+        <v>60</v>
+      </c>
+      <c r="F18" s="7">
+        <v>58</v>
+      </c>
+      <c r="G18" s="7">
+        <v>64</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="7">
+        <v>73</v>
+      </c>
+      <c r="D19" s="7">
+        <v>77</v>
+      </c>
+      <c r="E19" s="7">
+        <v>75</v>
+      </c>
+      <c r="F19" s="7">
+        <v>72</v>
+      </c>
+      <c r="G19" s="7">
+        <v>79</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="7">
+        <v>44</v>
+      </c>
+      <c r="D20" s="7">
+        <v>48</v>
+      </c>
+      <c r="E20" s="7">
+        <v>45</v>
+      </c>
+      <c r="F20" s="7">
+        <v>46</v>
+      </c>
+      <c r="G20" s="7">
+        <v>50</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="5" cm="1">
+        <f t="array" ref="M20">_xlfn.XLOOKUP(L20,B2:B51,_xlfn.XLOOKUP(M19,C1:G1,C2:G51))</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="7">
+        <v>88</v>
+      </c>
+      <c r="D21" s="7">
+        <v>90</v>
+      </c>
+      <c r="E21" s="7">
+        <v>89</v>
+      </c>
+      <c r="F21" s="7">
+        <v>87</v>
+      </c>
+      <c r="G21" s="7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="7">
+        <v>51</v>
+      </c>
+      <c r="D22" s="7">
+        <v>54</v>
+      </c>
+      <c r="E22" s="7">
+        <v>52</v>
+      </c>
+      <c r="F22" s="7">
+        <v>50</v>
+      </c>
+      <c r="G22" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A23" s="7">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="7">
+        <v>79</v>
+      </c>
+      <c r="D23" s="7">
+        <v>82</v>
+      </c>
+      <c r="E23" s="7">
+        <v>80</v>
+      </c>
+      <c r="F23" s="7">
+        <v>78</v>
+      </c>
+      <c r="G23" s="7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="7">
+        <v>63</v>
+      </c>
+      <c r="D24" s="7">
+        <v>66</v>
+      </c>
+      <c r="E24" s="7">
+        <v>64</v>
+      </c>
+      <c r="F24" s="7">
+        <v>62</v>
+      </c>
+      <c r="G24" s="7">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="7">
+        <v>39</v>
+      </c>
+      <c r="D25" s="7">
+        <v>42</v>
+      </c>
+      <c r="E25" s="7">
+        <v>40</v>
+      </c>
+      <c r="F25" s="7">
+        <v>38</v>
+      </c>
+      <c r="G25" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A26" s="7">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="7">
+        <v>85</v>
+      </c>
+      <c r="D26" s="7">
+        <v>88</v>
+      </c>
+      <c r="E26" s="7">
+        <v>87</v>
+      </c>
+      <c r="F26" s="7">
+        <v>84</v>
+      </c>
+      <c r="G26" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A27" s="7">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="7">
+        <v>56</v>
+      </c>
+      <c r="D27" s="7">
+        <v>59</v>
+      </c>
+      <c r="E27" s="7">
+        <v>58</v>
+      </c>
+      <c r="F27" s="7">
+        <v>55</v>
+      </c>
+      <c r="G27" s="7">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A28" s="7">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="7">
+        <v>72</v>
+      </c>
+      <c r="D28" s="7">
+        <v>75</v>
+      </c>
+      <c r="E28" s="7">
+        <v>73</v>
+      </c>
+      <c r="F28" s="7">
+        <v>71</v>
+      </c>
+      <c r="G28" s="7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A29" s="7">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="7">
+        <v>33</v>
+      </c>
+      <c r="D29" s="7">
+        <v>36</v>
+      </c>
+      <c r="E29" s="7">
+        <v>35</v>
+      </c>
+      <c r="F29" s="7">
+        <v>34</v>
+      </c>
+      <c r="G29" s="7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A30" s="7">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="7">
+        <v>66</v>
+      </c>
+      <c r="D30" s="7">
+        <v>69</v>
+      </c>
+      <c r="E30" s="7">
+        <v>67</v>
+      </c>
+      <c r="F30" s="7">
+        <v>65</v>
+      </c>
+      <c r="G30" s="7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A31" s="7">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="7">
+        <v>91</v>
+      </c>
+      <c r="D31" s="7">
+        <v>94</v>
+      </c>
+      <c r="E31" s="7">
+        <v>92</v>
+      </c>
+      <c r="F31" s="7">
+        <v>90</v>
+      </c>
+      <c r="G31" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A32" s="7">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="7">
+        <v>48</v>
+      </c>
+      <c r="D32" s="7">
+        <v>50</v>
+      </c>
+      <c r="E32" s="7">
+        <v>49</v>
+      </c>
+      <c r="F32" s="7">
+        <v>47</v>
+      </c>
+      <c r="G32" s="7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="7">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="7">
+        <v>77</v>
+      </c>
+      <c r="D33" s="7">
+        <v>80</v>
+      </c>
+      <c r="E33" s="7">
+        <v>78</v>
+      </c>
+      <c r="F33" s="7">
+        <v>76</v>
+      </c>
+      <c r="G33" s="7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="7">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="7">
+        <v>60</v>
+      </c>
+      <c r="D34" s="7">
+        <v>63</v>
+      </c>
+      <c r="E34" s="7">
+        <v>61</v>
+      </c>
+      <c r="F34" s="7">
+        <v>59</v>
+      </c>
+      <c r="G34" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="7">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="7">
+        <v>42</v>
+      </c>
+      <c r="D35" s="7">
+        <v>45</v>
+      </c>
+      <c r="E35" s="7">
+        <v>43</v>
+      </c>
+      <c r="F35" s="7">
+        <v>41</v>
+      </c>
+      <c r="G35" s="7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="7">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="7">
+        <v>84</v>
+      </c>
+      <c r="D36" s="7">
+        <v>87</v>
+      </c>
+      <c r="E36" s="7">
+        <v>85</v>
+      </c>
+      <c r="F36" s="7">
+        <v>82</v>
+      </c>
+      <c r="G36" s="7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="7">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="7">
+        <v>55</v>
+      </c>
+      <c r="D37" s="7">
+        <v>58</v>
+      </c>
+      <c r="E37" s="7">
+        <v>56</v>
+      </c>
+      <c r="F37" s="7">
+        <v>54</v>
+      </c>
+      <c r="G37" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="7">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="7">
+        <v>70</v>
+      </c>
+      <c r="D38" s="7">
+        <v>73</v>
+      </c>
+      <c r="E38" s="7">
+        <v>71</v>
+      </c>
+      <c r="F38" s="7">
+        <v>69</v>
+      </c>
+      <c r="G38" s="7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="7">
+        <v>36</v>
+      </c>
+      <c r="D39" s="7">
+        <v>39</v>
+      </c>
+      <c r="E39" s="7">
+        <v>38</v>
+      </c>
+      <c r="F39" s="7">
+        <v>37</v>
+      </c>
+      <c r="G39" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="7">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="7">
+        <v>64</v>
+      </c>
+      <c r="D40" s="7">
+        <v>67</v>
+      </c>
+      <c r="E40" s="7">
+        <v>65</v>
+      </c>
+      <c r="F40" s="7">
+        <v>63</v>
+      </c>
+      <c r="G40" s="7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="7">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="7">
+        <v>78</v>
+      </c>
+      <c r="D41" s="7">
+        <v>81</v>
+      </c>
+      <c r="E41" s="7">
+        <v>79</v>
+      </c>
+      <c r="F41" s="7">
+        <v>77</v>
+      </c>
+      <c r="G41" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="7">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="7">
+        <v>46</v>
+      </c>
+      <c r="D42" s="7">
+        <v>49</v>
+      </c>
+      <c r="E42" s="7">
+        <v>47</v>
+      </c>
+      <c r="F42" s="7">
+        <v>45</v>
+      </c>
+      <c r="G42" s="7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="7">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="7">
+        <v>86</v>
+      </c>
+      <c r="D43" s="7">
+        <v>89</v>
+      </c>
+      <c r="E43" s="7">
+        <v>88</v>
+      </c>
+      <c r="F43" s="7">
+        <v>85</v>
+      </c>
+      <c r="G43" s="7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="7">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="7">
+        <v>57</v>
+      </c>
+      <c r="D44" s="7">
+        <v>60</v>
+      </c>
+      <c r="E44" s="7">
+        <v>58</v>
+      </c>
+      <c r="F44" s="7">
+        <v>56</v>
+      </c>
+      <c r="G44" s="7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="7">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="7">
+        <v>40</v>
+      </c>
+      <c r="D45" s="7">
+        <v>43</v>
+      </c>
+      <c r="E45" s="7">
+        <v>41</v>
+      </c>
+      <c r="F45" s="7">
+        <v>39</v>
+      </c>
+      <c r="G45" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="7">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="7">
+        <v>83</v>
+      </c>
+      <c r="D46" s="7">
+        <v>86</v>
+      </c>
+      <c r="E46" s="7">
+        <v>84</v>
+      </c>
+      <c r="F46" s="7">
+        <v>82</v>
+      </c>
+      <c r="G46" s="7">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="7">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="7">
+        <v>69</v>
+      </c>
+      <c r="D47" s="7">
+        <v>72</v>
+      </c>
+      <c r="E47" s="7">
+        <v>70</v>
+      </c>
+      <c r="F47" s="7">
+        <v>68</v>
+      </c>
+      <c r="G47" s="7">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="7">
+        <v>47</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="7">
+        <v>52</v>
+      </c>
+      <c r="D48" s="7">
+        <v>55</v>
+      </c>
+      <c r="E48" s="7">
+        <v>53</v>
+      </c>
+      <c r="F48" s="7">
+        <v>51</v>
+      </c>
+      <c r="G48" s="7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="7">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="7">
+        <v>90</v>
+      </c>
+      <c r="D49" s="7">
+        <v>93</v>
+      </c>
+      <c r="E49" s="7">
+        <v>91</v>
+      </c>
+      <c r="F49" s="7">
+        <v>89</v>
+      </c>
+      <c r="G49" s="7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" s="7">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="7">
+        <v>61</v>
+      </c>
+      <c r="D50" s="7">
+        <v>64</v>
+      </c>
+      <c r="E50" s="7">
+        <v>62</v>
+      </c>
+      <c r="F50" s="7">
+        <v>60</v>
+      </c>
+      <c r="G50" s="7">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="7">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="7">
+        <v>75</v>
+      </c>
+      <c r="D51" s="7">
+        <v>78</v>
+      </c>
+      <c r="E51" s="7">
+        <v>76</v>
+      </c>
+      <c r="F51" s="7">
+        <v>74</v>
+      </c>
+      <c r="G51" s="7">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="L17:M18"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="O3:P4"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J7 M5 M19" xr:uid="{DECCFCF7-C88A-4C2B-811F-7E6697450708}">
+      <formula1>$C$1:$G$1</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8 I14 L6 L20" xr:uid="{1F002AC6-2C85-4CDA-8CDA-4FCC69BFE566}">
+      <formula1>$B$2:$B$51</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC346B93-613A-4146-A7A4-F1F5480B90F8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>